--- a/artfynd/A 39867-2025 artfynd.xlsx
+++ b/artfynd/A 39867-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602324</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602307</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602323</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602308</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602311</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602313</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1458,6 +1493,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602317</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602322</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602331</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,6 +1841,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602349</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1902,6 +1957,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602356</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2013,6 +2073,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602305</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2124,6 +2189,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602346</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2235,6 +2305,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602347</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2346,6 +2421,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602309</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2457,6 +2537,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602339</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2568,6 +2653,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602341</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2679,6 +2769,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602312</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2790,6 +2885,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602328</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2901,6 +3001,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602338</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3020,6 +3125,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602327</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3131,6 +3241,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602334</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3242,6 +3357,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602350</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3361,6 +3481,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602352</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3472,6 +3597,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602355</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3583,6 +3713,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602329</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3694,6 +3829,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602310</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3810,6 +3950,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602326</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3921,6 +4066,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602330</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4032,6 +4182,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602343</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4143,6 +4298,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602351</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4254,6 +4414,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602353</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4370,6 +4535,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602318</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4486,6 +4656,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602304</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4602,6 +4777,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602320</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4718,6 +4898,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602325</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4834,6 +5019,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602332</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4950,6 +5140,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602340</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5066,6 +5261,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602345</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5182,6 +5382,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602354</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5298,6 +5503,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602357</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5421,6 +5631,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602344</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5532,6 +5747,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602321</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5643,6 +5863,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602333</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5771,6 +5996,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602306</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5882,6 +6112,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602319</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5993,6 +6228,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602342</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6104,6 +6344,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602314</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6215,8 +6460,64 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134602348</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>